--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/PYTHON/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B28D8D-F904-4773-9B0B-37EEE82A038F}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A16B1D90-2837-4FDE-8111-E25E392DDD33}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,6 +231,18 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Work hard </t>
+  </si>
+  <si>
+    <t>Looks forwarding</t>
+  </si>
+  <si>
+    <t>Work hard</t>
   </si>
 </sst>
 </file>
@@ -1277,19 +1289,19 @@
         <v>40</v>
       </c>
       <c r="F12" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G12" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1030</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>57</v>
@@ -1421,95 +1433,177 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
       <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
+      <c r="D16" s="14">
+        <v>410</v>
+      </c>
+      <c r="E16" s="14">
+        <v>50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
       <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
+      <c r="D17" s="14">
+        <v>275</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>240</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
       <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>385</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
       <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>420</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
       <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="14">
+        <v>300</v>
+      </c>
       <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
+      <c r="D19" s="14">
+        <v>200</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>420</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
       <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46268</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/PYTHON/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A16B1D90-2837-4FDE-8111-E25E392DDD33}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8130E1EF-ACFB-4C40-BDBD-F3BDF079432F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,6 +243,27 @@
   </si>
   <si>
     <t>Work hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today was my presentation that was really awesome. </t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Today I  suffurinig from fever and cold but I still word hard.</t>
+  </si>
+  <si>
+    <t>Not well.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Distrubed</t>
   </si>
 </sst>
 </file>
@@ -1600,208 +1621,388 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>46268</v>
       </c>
-      <c r="B20" s="14"/>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
       <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
+      <c r="D20" s="14">
+        <v>210</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>240</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
       <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
       <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="D21" s="14">
+        <v>195</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
       <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
       <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="D22" s="14">
+        <v>420</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
       <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="D23" s="14">
+        <v>315</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>615</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
+      <c r="A24" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
       <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>240</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
       <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
       <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
+      <c r="D25" s="14">
+        <v>150</v>
+      </c>
+      <c r="E25" s="14">
+        <v>40</v>
+      </c>
+      <c r="F25" s="14">
+        <v>420</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
       <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
+        <v>410</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B26" s="14">
+        <v>300</v>
+      </c>
       <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
+      <c r="D26" s="14">
+        <v>205</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>120</v>
+      </c>
+      <c r="G26" s="14">
+        <v>2</v>
+      </c>
       <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>815</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
       <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>240</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
       <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
       <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>180</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
       <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13">
+        <v>46277</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1823,7 +2024,9 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46278</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -1845,7 +2048,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13">
+        <v>46279</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -1867,7 +2072,9 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13">
+        <v>46280</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -1889,7 +2096,9 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46281</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -1911,7 +2120,9 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
+      <c r="A34" s="13">
+        <v>46282</v>
+      </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
@@ -1933,7 +2144,9 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13">
+        <v>46283</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
@@ -1955,7 +2168,9 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46284</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -1977,7 +2192,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46285</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -1999,7 +2216,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46286</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2021,7 +2240,9 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13">
+        <v>46287</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2043,7 +2264,9 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
+      <c r="A40" s="13">
+        <v>46288</v>
+      </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -2065,7 +2288,9 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13">
+        <v>46289</v>
+      </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2087,7 +2312,9 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
+      <c r="A42" s="13">
+        <v>46290</v>
+      </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -2109,7 +2336,9 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
+      <c r="A43" s="13">
+        <v>46291</v>
+      </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2131,7 +2360,9 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
+      <c r="A44" s="13">
+        <v>46292</v>
+      </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -2153,7 +2384,9 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
+      <c r="A45" s="13">
+        <v>46293</v>
+      </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -2175,7 +2408,9 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
+      <c r="A46" s="13">
+        <v>46294</v>
+      </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2197,7 +2432,9 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
+      <c r="A47" s="13">
+        <v>46295</v>
+      </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2219,7 +2456,9 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
+      <c r="A48" s="13">
+        <v>46296</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2241,7 +2480,9 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
+      <c r="A49" s="13">
+        <v>46297</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2263,7 +2504,9 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
+      <c r="A50" s="13">
+        <v>46298</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2285,7 +2528,9 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
+      <c r="A51" s="13">
+        <v>46299</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2307,7 +2552,9 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13">
+        <v>46300</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2329,7 +2576,9 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
+      <c r="A53" s="13">
+        <v>46301</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2351,7 +2600,9 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
+      <c r="A54" s="13">
+        <v>46302</v>
+      </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2373,7 +2624,9 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
+      <c r="A55" s="13">
+        <v>46303</v>
+      </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2395,7 +2648,9 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
+      <c r="A56" s="13">
+        <v>46304</v>
+      </c>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -2417,7 +2672,9 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
+      <c r="A57" s="13">
+        <v>46305</v>
+      </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2439,7 +2696,9 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
+      <c r="A58" s="13">
+        <v>46306</v>
+      </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2461,7 +2720,9 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
+      <c r="A59" s="13">
+        <v>46307</v>
+      </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2483,7 +2744,9 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
+      <c r="A60" s="13">
+        <v>46308</v>
+      </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -2505,7 +2768,9 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
+      <c r="A61" s="13">
+        <v>46309</v>
+      </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -2527,7 +2792,9 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
+      <c r="A62" s="13">
+        <v>46310</v>
+      </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -2549,7 +2816,9 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
+      <c r="A63" s="13">
+        <v>46311</v>
+      </c>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -2571,7 +2840,9 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
+      <c r="A64" s="13">
+        <v>46312</v>
+      </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -2593,7 +2864,9 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
+      <c r="A65" s="13">
+        <v>46313</v>
+      </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2615,7 +2888,9 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
+      <c r="A66" s="13">
+        <v>46314</v>
+      </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -2637,7 +2912,9 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
+      <c r="A67" s="13">
+        <v>46315</v>
+      </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -2659,7 +2936,9 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
+      <c r="A68" s="13">
+        <v>46316</v>
+      </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -2681,7 +2960,9 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
+      <c r="A69" s="13">
+        <v>46317</v>
+      </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -2703,7 +2984,9 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
+      <c r="A70" s="13">
+        <v>46318</v>
+      </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -2725,7 +3008,9 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
+      <c r="A71" s="13">
+        <v>46319</v>
+      </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -2747,7 +3032,9 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
+      <c r="A72" s="13">
+        <v>46320</v>
+      </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -2769,7 +3056,9 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
+      <c r="A73" s="13">
+        <v>46321</v>
+      </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -2791,7 +3080,9 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
+      <c r="A74" s="13">
+        <v>46322</v>
+      </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -2813,7 +3104,9 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
+      <c r="A75" s="13">
+        <v>46323</v>
+      </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -2835,7 +3128,9 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
+      <c r="A76" s="13">
+        <v>46324</v>
+      </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -2857,7 +3152,9 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
+      <c r="A77" s="13">
+        <v>46325</v>
+      </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -2879,7 +3176,9 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
+      <c r="A78" s="13">
+        <v>46326</v>
+      </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -2901,7 +3200,9 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="13"/>
+      <c r="A79" s="13">
+        <v>46327</v>
+      </c>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -2923,7 +3224,9 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="13"/>
+      <c r="A80" s="13">
+        <v>46328</v>
+      </c>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -2945,7 +3248,9 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13"/>
+      <c r="A81" s="13">
+        <v>46329</v>
+      </c>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -2967,7 +3272,9 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="13"/>
+      <c r="A82" s="13">
+        <v>46330</v>
+      </c>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -2989,7 +3296,9 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="13"/>
+      <c r="A83" s="13">
+        <v>46331</v>
+      </c>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -3011,7 +3320,9 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="13"/>
+      <c r="A84" s="13">
+        <v>46332</v>
+      </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -3033,7 +3344,9 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="13"/>
+      <c r="A85" s="13">
+        <v>46333</v>
+      </c>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -3055,7 +3368,9 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" s="13"/>
+      <c r="A86" s="13">
+        <v>46334</v>
+      </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -3077,7 +3392,9 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A87" s="13"/>
+      <c r="A87" s="13">
+        <v>46335</v>
+      </c>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -3099,7 +3416,9 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A88" s="13"/>
+      <c r="A88" s="13">
+        <v>46336</v>
+      </c>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3121,7 +3440,9 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A89" s="13"/>
+      <c r="A89" s="13">
+        <v>46337</v>
+      </c>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -3143,7 +3464,9 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A90" s="13"/>
+      <c r="A90" s="13">
+        <v>46338</v>
+      </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -3165,7 +3488,9 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A91" s="13"/>
+      <c r="A91" s="13">
+        <v>46339</v>
+      </c>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -3187,7 +3512,9 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A92" s="13"/>
+      <c r="A92" s="13">
+        <v>46340</v>
+      </c>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -3209,7 +3536,9 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A93" s="13"/>
+      <c r="A93" s="13">
+        <v>46341</v>
+      </c>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -3231,7 +3560,9 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A94" s="13"/>
+      <c r="A94" s="13">
+        <v>46342</v>
+      </c>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -3253,7 +3584,9 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A95" s="13"/>
+      <c r="A95" s="13">
+        <v>46343</v>
+      </c>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -3275,7 +3608,9 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A96" s="13"/>
+      <c r="A96" s="13">
+        <v>46344</v>
+      </c>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -3297,7 +3632,9 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A97" s="13"/>
+      <c r="A97" s="13">
+        <v>46345</v>
+      </c>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -3319,7 +3656,9 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A98" s="13"/>
+      <c r="A98" s="13">
+        <v>46346</v>
+      </c>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -3341,7 +3680,9 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A99" s="13"/>
+      <c r="A99" s="13">
+        <v>46347</v>
+      </c>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -3363,7 +3704,9 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A100" s="13"/>
+      <c r="A100" s="13">
+        <v>46348</v>
+      </c>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -3385,7 +3728,9 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A101" s="13"/>
+      <c r="A101" s="13">
+        <v>46349</v>
+      </c>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -3407,7 +3752,9 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A102" s="13"/>
+      <c r="A102" s="13">
+        <v>46350</v>
+      </c>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -3429,7 +3776,9 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A103" s="13"/>
+      <c r="A103" s="13">
+        <v>46351</v>
+      </c>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -3451,7 +3800,9 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A104" s="13"/>
+      <c r="A104" s="13">
+        <v>46352</v>
+      </c>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -3473,7 +3824,9 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A105" s="13"/>
+      <c r="A105" s="13">
+        <v>46353</v>
+      </c>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -3495,7 +3848,9 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A106" s="13"/>
+      <c r="A106" s="13">
+        <v>46354</v>
+      </c>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -3517,7 +3872,9 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A107" s="13"/>
+      <c r="A107" s="13">
+        <v>46355</v>
+      </c>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -3539,7 +3896,9 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A108" s="13"/>
+      <c r="A108" s="13">
+        <v>46356</v>
+      </c>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -3561,7 +3920,9 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A109" s="13"/>
+      <c r="A109" s="13">
+        <v>46357</v>
+      </c>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -3583,7 +3944,9 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A110" s="13"/>
+      <c r="A110" s="13">
+        <v>46358</v>
+      </c>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -3605,7 +3968,9 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A111" s="13"/>
+      <c r="A111" s="13">
+        <v>46359</v>
+      </c>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -3627,7 +3992,9 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A112" s="13"/>
+      <c r="A112" s="13">
+        <v>46360</v>
+      </c>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -3649,7 +4016,9 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="13"/>
+      <c r="A113" s="13">
+        <v>46361</v>
+      </c>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -3671,7 +4040,9 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="13"/>
+      <c r="A114" s="13">
+        <v>46362</v>
+      </c>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -3693,7 +4064,9 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="13"/>
+      <c r="A115" s="13">
+        <v>46363</v>
+      </c>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -3715,7 +4088,9 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="13"/>
+      <c r="A116" s="13">
+        <v>46364</v>
+      </c>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -3737,7 +4112,9 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="13"/>
+      <c r="A117" s="13">
+        <v>46365</v>
+      </c>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -3759,7 +4136,9 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A118" s="13"/>
+      <c r="A118" s="13">
+        <v>46366</v>
+      </c>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -3781,7 +4160,9 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A119" s="13"/>
+      <c r="A119" s="13">
+        <v>46367</v>
+      </c>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -3803,7 +4184,9 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A120" s="13"/>
+      <c r="A120" s="13">
+        <v>46368</v>
+      </c>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -3825,7 +4208,9 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="13"/>
+      <c r="A121" s="13">
+        <v>46369</v>
+      </c>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -3847,7 +4232,9 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A122" s="13"/>
+      <c r="A122" s="13">
+        <v>46370</v>
+      </c>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -3869,7 +4256,9 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A123" s="13"/>
+      <c r="A123" s="13">
+        <v>46371</v>
+      </c>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -3891,7 +4280,9 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A124" s="13"/>
+      <c r="A124" s="13">
+        <v>46372</v>
+      </c>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -3913,7 +4304,9 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A125" s="13"/>
+      <c r="A125" s="13">
+        <v>46373</v>
+      </c>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -3935,7 +4328,9 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A126" s="13"/>
+      <c r="A126" s="13">
+        <v>46374</v>
+      </c>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -3957,7 +4352,9 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A127" s="13"/>
+      <c r="A127" s="13">
+        <v>46375</v>
+      </c>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -3979,7 +4376,9 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="13"/>
+      <c r="A128" s="13">
+        <v>46376</v>
+      </c>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4001,7 +4400,9 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A129" s="13"/>
+      <c r="A129" s="13">
+        <v>46377</v>
+      </c>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4023,7 +4424,9 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A130" s="13"/>
+      <c r="A130" s="13">
+        <v>46378</v>
+      </c>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4045,7 +4448,9 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A131" s="13"/>
+      <c r="A131" s="13">
+        <v>46379</v>
+      </c>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -4067,7 +4472,9 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A132" s="13"/>
+      <c r="A132" s="13">
+        <v>46380</v>
+      </c>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -4089,7 +4496,9 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A133" s="13"/>
+      <c r="A133" s="13">
+        <v>46381</v>
+      </c>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -4111,7 +4520,9 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A134" s="13"/>
+      <c r="A134" s="13">
+        <v>46382</v>
+      </c>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -4133,7 +4544,9 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A135" s="13"/>
+      <c r="A135" s="13">
+        <v>46383</v>
+      </c>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -4155,7 +4568,9 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A136" s="13"/>
+      <c r="A136" s="13">
+        <v>46384</v>
+      </c>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -4177,7 +4592,9 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A137" s="13"/>
+      <c r="A137" s="13">
+        <v>46385</v>
+      </c>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -4199,7 +4616,9 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A138" s="13"/>
+      <c r="A138" s="13">
+        <v>46386</v>
+      </c>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -4221,7 +4640,9 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A139" s="13"/>
+      <c r="A139" s="13">
+        <v>46387</v>
+      </c>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -4243,7 +4664,9 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A140" s="13"/>
+      <c r="A140" s="13">
+        <v>46388</v>
+      </c>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -4265,7 +4688,9 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A141" s="13"/>
+      <c r="A141" s="13">
+        <v>46389</v>
+      </c>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4287,7 +4712,9 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A142" s="13"/>
+      <c r="A142" s="13">
+        <v>46390</v>
+      </c>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4309,7 +4736,9 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A143" s="13"/>
+      <c r="A143" s="13">
+        <v>46391</v>
+      </c>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4331,7 +4760,9 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A144" s="13"/>
+      <c r="A144" s="13">
+        <v>46392</v>
+      </c>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4353,7 +4784,9 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A145" s="13"/>
+      <c r="A145" s="13">
+        <v>46393</v>
+      </c>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -4375,7 +4808,9 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A146" s="13"/>
+      <c r="A146" s="13">
+        <v>46394</v>
+      </c>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -4397,7 +4832,9 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A147" s="13"/>
+      <c r="A147" s="13">
+        <v>46395</v>
+      </c>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -4419,7 +4856,9 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A148" s="13"/>
+      <c r="A148" s="13">
+        <v>46396</v>
+      </c>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -4441,7 +4880,9 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A149" s="13"/>
+      <c r="A149" s="13">
+        <v>46397</v>
+      </c>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -4463,7 +4904,9 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A150" s="13"/>
+      <c r="A150" s="13">
+        <v>46398</v>
+      </c>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -4485,7 +4928,9 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A151" s="13"/>
+      <c r="A151" s="13">
+        <v>46399</v>
+      </c>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -4507,7 +4952,9 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A152" s="13"/>
+      <c r="A152" s="13">
+        <v>46400</v>
+      </c>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -4529,7 +4976,9 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A153" s="13"/>
+      <c r="A153" s="13">
+        <v>46401</v>
+      </c>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -4551,7 +5000,9 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A154" s="13"/>
+      <c r="A154" s="13">
+        <v>46402</v>
+      </c>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -4573,7 +5024,9 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A155" s="13"/>
+      <c r="A155" s="13">
+        <v>46403</v>
+      </c>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -4595,7 +5048,9 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A156" s="13"/>
+      <c r="A156" s="13">
+        <v>46404</v>
+      </c>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -4617,7 +5072,9 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A157" s="13"/>
+      <c r="A157" s="13">
+        <v>46405</v>
+      </c>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -4639,7 +5096,9 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A158" s="13"/>
+      <c r="A158" s="13">
+        <v>46406</v>
+      </c>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -4661,7 +5120,9 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A159" s="13"/>
+      <c r="A159" s="13">
+        <v>46407</v>
+      </c>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -4683,7 +5144,9 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A160" s="13"/>
+      <c r="A160" s="13">
+        <v>46408</v>
+      </c>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -4705,7 +5168,9 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A161" s="13"/>
+      <c r="A161" s="13">
+        <v>46409</v>
+      </c>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -4727,7 +5192,9 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A162" s="13"/>
+      <c r="A162" s="13">
+        <v>46410</v>
+      </c>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -4749,7 +5216,9 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A163" s="13"/>
+      <c r="A163" s="13">
+        <v>46411</v>
+      </c>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -4771,7 +5240,9 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A164" s="13"/>
+      <c r="A164" s="13">
+        <v>46412</v>
+      </c>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -4793,7 +5264,9 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A165" s="13"/>
+      <c r="A165" s="13">
+        <v>46413</v>
+      </c>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -4815,7 +5288,9 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A166" s="13"/>
+      <c r="A166" s="13">
+        <v>46414</v>
+      </c>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -4837,7 +5312,9 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A167" s="13"/>
+      <c r="A167" s="13">
+        <v>46415</v>
+      </c>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -4859,7 +5336,9 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A168" s="13"/>
+      <c r="A168" s="13">
+        <v>46416</v>
+      </c>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -4881,7 +5360,9 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A169" s="13"/>
+      <c r="A169" s="13">
+        <v>46417</v>
+      </c>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -4903,7 +5384,9 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A170" s="13"/>
+      <c r="A170" s="13">
+        <v>46418</v>
+      </c>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -4925,7 +5408,9 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A171" s="13"/>
+      <c r="A171" s="13">
+        <v>46419</v>
+      </c>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -4947,7 +5432,9 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A172" s="13"/>
+      <c r="A172" s="13">
+        <v>46420</v>
+      </c>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -4969,7 +5456,9 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A173" s="13"/>
+      <c r="A173" s="13">
+        <v>46421</v>
+      </c>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -4991,7 +5480,9 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A174" s="13"/>
+      <c r="A174" s="13">
+        <v>46422</v>
+      </c>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5013,7 +5504,9 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A175" s="13"/>
+      <c r="A175" s="13">
+        <v>46423</v>
+      </c>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5035,7 +5528,9 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A176" s="13"/>
+      <c r="A176" s="13">
+        <v>46424</v>
+      </c>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5057,7 +5552,9 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A177" s="13"/>
+      <c r="A177" s="13">
+        <v>46425</v>
+      </c>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -5079,7 +5576,9 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A178" s="13"/>
+      <c r="A178" s="13">
+        <v>46426</v>
+      </c>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -5101,7 +5600,9 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A179" s="13"/>
+      <c r="A179" s="13">
+        <v>46427</v>
+      </c>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -5123,7 +5624,9 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A180" s="13"/>
+      <c r="A180" s="13">
+        <v>46428</v>
+      </c>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -5145,7 +5648,9 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A181" s="13"/>
+      <c r="A181" s="13">
+        <v>46429</v>
+      </c>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -5167,7 +5672,9 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A182" s="13"/>
+      <c r="A182" s="13">
+        <v>46430</v>
+      </c>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -5189,7 +5696,9 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A183" s="13"/>
+      <c r="A183" s="13">
+        <v>46431</v>
+      </c>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -5211,7 +5720,9 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A184" s="13"/>
+      <c r="A184" s="13">
+        <v>46432</v>
+      </c>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5233,7 +5744,9 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A185" s="13"/>
+      <c r="A185" s="13">
+        <v>46433</v>
+      </c>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5255,7 +5768,9 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A186" s="13"/>
+      <c r="A186" s="13">
+        <v>46434</v>
+      </c>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -5277,7 +5792,9 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A187" s="13"/>
+      <c r="A187" s="13">
+        <v>46435</v>
+      </c>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -5299,7 +5816,9 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A188" s="13"/>
+      <c r="A188" s="13">
+        <v>46436</v>
+      </c>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -5321,7 +5840,9 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A189" s="13"/>
+      <c r="A189" s="13">
+        <v>46437</v>
+      </c>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -5343,7 +5864,9 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A190" s="13"/>
+      <c r="A190" s="13">
+        <v>46438</v>
+      </c>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -5365,7 +5888,9 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A191" s="13"/>
+      <c r="A191" s="13">
+        <v>46439</v>
+      </c>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -5387,7 +5912,9 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A192" s="13"/>
+      <c r="A192" s="13">
+        <v>46440</v>
+      </c>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -5409,7 +5936,9 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A193" s="13"/>
+      <c r="A193" s="13">
+        <v>46441</v>
+      </c>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -5431,7 +5960,9 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A194" s="13"/>
+      <c r="A194" s="13">
+        <v>46442</v>
+      </c>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -5453,7 +5984,9 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A195" s="13"/>
+      <c r="A195" s="13">
+        <v>46443</v>
+      </c>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -5475,7 +6008,9 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A196" s="13"/>
+      <c r="A196" s="13">
+        <v>46444</v>
+      </c>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -5497,7 +6032,9 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A197" s="13"/>
+      <c r="A197" s="13">
+        <v>46445</v>
+      </c>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -5519,7 +6056,9 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A198" s="13"/>
+      <c r="A198" s="13">
+        <v>46446</v>
+      </c>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -5541,7 +6080,9 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A199" s="13"/>
+      <c r="A199" s="13">
+        <v>46447</v>
+      </c>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -5563,7 +6104,9 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A200" s="13"/>
+      <c r="A200" s="13">
+        <v>46448</v>
+      </c>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -5585,7 +6128,9 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A201" s="13"/>
+      <c r="A201" s="13">
+        <v>46449</v>
+      </c>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -5607,7 +6152,9 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A202" s="13"/>
+      <c r="A202" s="13">
+        <v>46450</v>
+      </c>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -5629,7 +6176,9 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A203" s="13"/>
+      <c r="A203" s="13">
+        <v>46451</v>
+      </c>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -5651,7 +6200,9 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A204" s="13"/>
+      <c r="A204" s="13">
+        <v>46452</v>
+      </c>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -5673,7 +6224,9 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A205" s="13"/>
+      <c r="A205" s="13">
+        <v>46453</v>
+      </c>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -5695,7 +6248,9 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A206" s="13"/>
+      <c r="A206" s="13">
+        <v>46454</v>
+      </c>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -5717,7 +6272,9 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A207" s="13"/>
+      <c r="A207" s="13">
+        <v>46455</v>
+      </c>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -5739,7 +6296,9 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A208" s="13"/>
+      <c r="A208" s="13">
+        <v>46456</v>
+      </c>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -5761,7 +6320,9 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A209" s="13"/>
+      <c r="A209" s="13">
+        <v>46457</v>
+      </c>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -5783,7 +6344,9 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A210" s="13"/>
+      <c r="A210" s="13">
+        <v>46458</v>
+      </c>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -5805,7 +6368,9 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A211" s="13"/>
+      <c r="A211" s="13">
+        <v>46459</v>
+      </c>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -5827,7 +6392,9 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A212" s="13"/>
+      <c r="A212" s="13">
+        <v>46460</v>
+      </c>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -5849,7 +6416,9 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A213" s="13"/>
+      <c r="A213" s="13">
+        <v>46461</v>
+      </c>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -5871,7 +6440,9 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A214" s="13"/>
+      <c r="A214" s="13">
+        <v>46462</v>
+      </c>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -5893,7 +6464,9 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A215" s="13"/>
+      <c r="A215" s="13">
+        <v>46463</v>
+      </c>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -5915,7 +6488,9 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A216" s="13"/>
+      <c r="A216" s="13">
+        <v>46464</v>
+      </c>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -5937,7 +6512,9 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A217" s="13"/>
+      <c r="A217" s="13">
+        <v>46465</v>
+      </c>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -5959,7 +6536,9 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A218" s="13"/>
+      <c r="A218" s="13">
+        <v>46466</v>
+      </c>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -5981,7 +6560,9 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A219" s="13"/>
+      <c r="A219" s="13">
+        <v>46467</v>
+      </c>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -6003,7 +6584,9 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A220" s="13"/>
+      <c r="A220" s="13">
+        <v>46468</v>
+      </c>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -6025,7 +6608,9 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A221" s="13"/>
+      <c r="A221" s="13">
+        <v>46469</v>
+      </c>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -6047,7 +6632,9 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A222" s="13"/>
+      <c r="A222" s="13">
+        <v>46470</v>
+      </c>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -6069,7 +6656,9 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A223" s="13"/>
+      <c r="A223" s="13">
+        <v>46471</v>
+      </c>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -6091,7 +6680,9 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A224" s="13"/>
+      <c r="A224" s="13">
+        <v>46472</v>
+      </c>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -6113,7 +6704,9 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A225" s="13"/>
+      <c r="A225" s="13">
+        <v>46473</v>
+      </c>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -6135,7 +6728,9 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A226" s="13"/>
+      <c r="A226" s="13">
+        <v>46474</v>
+      </c>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -6157,7 +6752,9 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A227" s="13"/>
+      <c r="A227" s="13">
+        <v>46475</v>
+      </c>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -6179,7 +6776,9 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A228" s="13"/>
+      <c r="A228" s="13">
+        <v>46476</v>
+      </c>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -6201,7 +6800,9 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A229" s="13"/>
+      <c r="A229" s="13">
+        <v>46477</v>
+      </c>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -6223,7 +6824,9 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A230" s="13"/>
+      <c r="A230" s="13">
+        <v>46478</v>
+      </c>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -6245,7 +6848,9 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A231" s="13"/>
+      <c r="A231" s="13">
+        <v>46479</v>
+      </c>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -6267,7 +6872,9 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A232" s="13"/>
+      <c r="A232" s="13">
+        <v>46480</v>
+      </c>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -6289,7 +6896,9 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A233" s="13"/>
+      <c r="A233" s="13">
+        <v>46481</v>
+      </c>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -6311,7 +6920,9 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A234" s="13"/>
+      <c r="A234" s="13">
+        <v>46482</v>
+      </c>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -6333,7 +6944,9 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A235" s="13"/>
+      <c r="A235" s="13">
+        <v>46483</v>
+      </c>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -6355,7 +6968,9 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A236" s="13"/>
+      <c r="A236" s="13">
+        <v>46484</v>
+      </c>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -6377,7 +6992,9 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A237" s="13"/>
+      <c r="A237" s="13">
+        <v>46485</v>
+      </c>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -6399,7 +7016,9 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A238" s="13"/>
+      <c r="A238" s="13">
+        <v>46486</v>
+      </c>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -6421,7 +7040,9 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A239" s="13"/>
+      <c r="A239" s="13">
+        <v>46487</v>
+      </c>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -6443,7 +7064,9 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A240" s="13"/>
+      <c r="A240" s="13">
+        <v>46488</v>
+      </c>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -6465,7 +7088,9 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A241" s="13"/>
+      <c r="A241" s="13">
+        <v>46489</v>
+      </c>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -6487,7 +7112,9 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A242" s="13"/>
+      <c r="A242" s="13">
+        <v>46490</v>
+      </c>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -6509,7 +7136,9 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A243" s="13"/>
+      <c r="A243" s="13">
+        <v>46491</v>
+      </c>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -6531,7 +7160,9 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A244" s="13"/>
+      <c r="A244" s="13">
+        <v>46492</v>
+      </c>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -6553,7 +7184,9 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A245" s="13"/>
+      <c r="A245" s="13">
+        <v>46493</v>
+      </c>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -6575,7 +7208,9 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A246" s="13"/>
+      <c r="A246" s="13">
+        <v>46494</v>
+      </c>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -6597,7 +7232,9 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A247" s="13"/>
+      <c r="A247" s="13">
+        <v>46495</v>
+      </c>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -6619,7 +7256,9 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A248" s="13"/>
+      <c r="A248" s="13">
+        <v>46496</v>
+      </c>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -6641,7 +7280,9 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A249" s="13"/>
+      <c r="A249" s="13">
+        <v>46497</v>
+      </c>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -6663,7 +7304,9 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A250" s="13"/>
+      <c r="A250" s="13">
+        <v>46498</v>
+      </c>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -6685,7 +7328,9 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A251" s="13"/>
+      <c r="A251" s="13">
+        <v>46499</v>
+      </c>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -6707,7 +7352,9 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A252" s="13"/>
+      <c r="A252" s="13">
+        <v>46500</v>
+      </c>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -6729,7 +7376,9 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A253" s="13"/>
+      <c r="A253" s="13">
+        <v>46501</v>
+      </c>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -6751,7 +7400,9 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A254" s="13"/>
+      <c r="A254" s="13">
+        <v>46502</v>
+      </c>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -6773,7 +7424,9 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A255" s="13"/>
+      <c r="A255" s="13">
+        <v>46503</v>
+      </c>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -6795,7 +7448,9 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A256" s="13"/>
+      <c r="A256" s="13">
+        <v>46504</v>
+      </c>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -6817,7 +7472,9 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A257" s="13"/>
+      <c r="A257" s="13">
+        <v>46505</v>
+      </c>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -6839,7 +7496,9 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A258" s="13"/>
+      <c r="A258" s="13">
+        <v>46506</v>
+      </c>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -6861,7 +7520,9 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A259" s="13"/>
+      <c r="A259" s="13">
+        <v>46507</v>
+      </c>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -6883,7 +7544,9 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A260" s="13"/>
+      <c r="A260" s="13">
+        <v>46508</v>
+      </c>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -6905,7 +7568,9 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A261" s="13"/>
+      <c r="A261" s="13">
+        <v>46509</v>
+      </c>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -6927,7 +7592,9 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A262" s="13"/>
+      <c r="A262" s="13">
+        <v>46510</v>
+      </c>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -6949,7 +7616,9 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A263" s="13"/>
+      <c r="A263" s="13">
+        <v>46511</v>
+      </c>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -6971,7 +7640,9 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A264" s="13"/>
+      <c r="A264" s="13">
+        <v>46512</v>
+      </c>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -6993,7 +7664,9 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A265" s="13"/>
+      <c r="A265" s="13">
+        <v>46513</v>
+      </c>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -7015,7 +7688,9 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A266" s="13"/>
+      <c r="A266" s="13">
+        <v>46514</v>
+      </c>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -7037,7 +7712,9 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A267" s="13"/>
+      <c r="A267" s="13">
+        <v>46515</v>
+      </c>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -7059,7 +7736,9 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A268" s="13"/>
+      <c r="A268" s="13">
+        <v>46516</v>
+      </c>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -7081,7 +7760,9 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A269" s="13"/>
+      <c r="A269" s="13">
+        <v>46517</v>
+      </c>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -7103,7 +7784,9 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A270" s="13"/>
+      <c r="A270" s="13">
+        <v>46518</v>
+      </c>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -7125,7 +7808,9 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A271" s="13"/>
+      <c r="A271" s="13">
+        <v>46519</v>
+      </c>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -7147,7 +7832,9 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A272" s="13"/>
+      <c r="A272" s="13">
+        <v>46520</v>
+      </c>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -7169,7 +7856,9 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A273" s="13"/>
+      <c r="A273" s="13">
+        <v>46521</v>
+      </c>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -7191,7 +7880,9 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A274" s="13"/>
+      <c r="A274" s="13">
+        <v>46522</v>
+      </c>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -7213,7 +7904,9 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A275" s="13"/>
+      <c r="A275" s="13">
+        <v>46523</v>
+      </c>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -7235,7 +7928,9 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A276" s="13"/>
+      <c r="A276" s="13">
+        <v>46524</v>
+      </c>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -7257,7 +7952,9 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A277" s="13"/>
+      <c r="A277" s="13">
+        <v>46525</v>
+      </c>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -7279,7 +7976,9 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A278" s="13"/>
+      <c r="A278" s="13">
+        <v>46526</v>
+      </c>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -7301,7 +8000,9 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A279" s="13"/>
+      <c r="A279" s="13">
+        <v>46527</v>
+      </c>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -7323,7 +8024,9 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A280" s="13"/>
+      <c r="A280" s="13">
+        <v>46528</v>
+      </c>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -7345,7 +8048,9 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A281" s="13"/>
+      <c r="A281" s="13">
+        <v>46529</v>
+      </c>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -7367,7 +8072,9 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A282" s="13"/>
+      <c r="A282" s="13">
+        <v>46530</v>
+      </c>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -7389,7 +8096,9 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A283" s="13"/>
+      <c r="A283" s="13">
+        <v>46531</v>
+      </c>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -7411,7 +8120,9 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A284" s="13"/>
+      <c r="A284" s="13">
+        <v>46532</v>
+      </c>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -7433,7 +8144,9 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A285" s="13"/>
+      <c r="A285" s="13">
+        <v>46533</v>
+      </c>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -7455,7 +8168,9 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A286" s="13"/>
+      <c r="A286" s="13">
+        <v>46534</v>
+      </c>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -7477,7 +8192,9 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A287" s="13"/>
+      <c r="A287" s="13">
+        <v>46535</v>
+      </c>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -7499,7 +8216,9 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A288" s="13"/>
+      <c r="A288" s="13">
+        <v>46536</v>
+      </c>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -7521,7 +8240,9 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A289" s="13"/>
+      <c r="A289" s="13">
+        <v>46537</v>
+      </c>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -7543,7 +8264,9 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A290" s="13"/>
+      <c r="A290" s="13">
+        <v>46538</v>
+      </c>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -7565,7 +8288,9 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A291" s="13"/>
+      <c r="A291" s="13">
+        <v>46539</v>
+      </c>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -7587,7 +8312,9 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A292" s="13"/>
+      <c r="A292" s="13">
+        <v>46540</v>
+      </c>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -7609,7 +8336,9 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A293" s="13"/>
+      <c r="A293" s="13">
+        <v>46541</v>
+      </c>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -7631,7 +8360,9 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A294" s="13"/>
+      <c r="A294" s="13">
+        <v>46542</v>
+      </c>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -7653,7 +8384,9 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A295" s="13"/>
+      <c r="A295" s="13">
+        <v>46543</v>
+      </c>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -7675,7 +8408,9 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A296" s="13"/>
+      <c r="A296" s="13">
+        <v>46544</v>
+      </c>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -7697,7 +8432,9 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A297" s="13"/>
+      <c r="A297" s="13">
+        <v>46545</v>
+      </c>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -7719,7 +8456,9 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A298" s="13"/>
+      <c r="A298" s="13">
+        <v>46546</v>
+      </c>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -7741,7 +8480,9 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A299" s="13"/>
+      <c r="A299" s="13">
+        <v>46547</v>
+      </c>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -7763,7 +8504,9 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A300" s="13"/>
+      <c r="A300" s="13">
+        <v>46548</v>
+      </c>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -7785,7 +8528,9 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A301" s="13"/>
+      <c r="A301" s="13">
+        <v>46549</v>
+      </c>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -7807,7 +8552,9 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A302" s="13"/>
+      <c r="A302" s="13">
+        <v>46550</v>
+      </c>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -7829,7 +8576,9 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A303" s="13"/>
+      <c r="A303" s="13">
+        <v>46551</v>
+      </c>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -7851,7 +8600,9 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A304" s="13"/>
+      <c r="A304" s="13">
+        <v>46552</v>
+      </c>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -7873,7 +8624,9 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A305" s="13"/>
+      <c r="A305" s="13">
+        <v>46553</v>
+      </c>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -7895,7 +8648,9 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A306" s="13"/>
+      <c r="A306" s="13">
+        <v>46554</v>
+      </c>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -7917,7 +8672,9 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A307" s="13"/>
+      <c r="A307" s="13">
+        <v>46555</v>
+      </c>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -7939,7 +8696,9 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A308" s="13"/>
+      <c r="A308" s="13">
+        <v>46556</v>
+      </c>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -7961,7 +8720,9 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A309" s="13"/>
+      <c r="A309" s="13">
+        <v>46557</v>
+      </c>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -7983,7 +8744,9 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A310" s="13"/>
+      <c r="A310" s="13">
+        <v>46558</v>
+      </c>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -8005,7 +8768,9 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A311" s="13"/>
+      <c r="A311" s="13">
+        <v>46559</v>
+      </c>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -8027,7 +8792,9 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A312" s="13"/>
+      <c r="A312" s="13">
+        <v>46560</v>
+      </c>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -8049,7 +8816,9 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A313" s="13"/>
+      <c r="A313" s="13">
+        <v>46561</v>
+      </c>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -8071,7 +8840,9 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A314" s="13"/>
+      <c r="A314" s="13">
+        <v>46562</v>
+      </c>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -8093,7 +8864,9 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A315" s="13"/>
+      <c r="A315" s="13">
+        <v>46563</v>
+      </c>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -8115,7 +8888,9 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A316" s="13"/>
+      <c r="A316" s="13">
+        <v>46564</v>
+      </c>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -8137,7 +8912,9 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A317" s="13"/>
+      <c r="A317" s="13">
+        <v>46565</v>
+      </c>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -8159,7 +8936,9 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A318" s="13"/>
+      <c r="A318" s="13">
+        <v>46566</v>
+      </c>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -8181,7 +8960,9 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A319" s="13"/>
+      <c r="A319" s="13">
+        <v>46567</v>
+      </c>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -8203,7 +8984,9 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A320" s="13"/>
+      <c r="A320" s="13">
+        <v>46568</v>
+      </c>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -8225,7 +9008,9 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A321" s="13"/>
+      <c r="A321" s="13">
+        <v>46569</v>
+      </c>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -8247,7 +9032,9 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A322" s="13"/>
+      <c r="A322" s="13">
+        <v>46570</v>
+      </c>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -8269,7 +9056,9 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A323" s="13"/>
+      <c r="A323" s="13">
+        <v>46571</v>
+      </c>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -8291,7 +9080,9 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A324" s="13"/>
+      <c r="A324" s="13">
+        <v>46572</v>
+      </c>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -8313,7 +9104,9 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A325" s="13"/>
+      <c r="A325" s="13">
+        <v>46573</v>
+      </c>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -8335,7 +9128,9 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A326" s="13"/>
+      <c r="A326" s="13">
+        <v>46574</v>
+      </c>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -8357,7 +9152,9 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A327" s="13"/>
+      <c r="A327" s="13">
+        <v>46575</v>
+      </c>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -8379,7 +9176,9 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A328" s="13"/>
+      <c r="A328" s="13">
+        <v>46576</v>
+      </c>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -8401,7 +9200,9 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A329" s="13"/>
+      <c r="A329" s="13">
+        <v>46577</v>
+      </c>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -8423,7 +9224,9 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A330" s="13"/>
+      <c r="A330" s="13">
+        <v>46578</v>
+      </c>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -8445,7 +9248,9 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A331" s="13"/>
+      <c r="A331" s="13">
+        <v>46579</v>
+      </c>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -8467,7 +9272,9 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A332" s="13"/>
+      <c r="A332" s="13">
+        <v>46580</v>
+      </c>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -8489,7 +9296,9 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A333" s="13"/>
+      <c r="A333" s="13">
+        <v>46581</v>
+      </c>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -8511,7 +9320,9 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A334" s="13"/>
+      <c r="A334" s="13">
+        <v>46582</v>
+      </c>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -8533,7 +9344,9 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A335" s="13"/>
+      <c r="A335" s="13">
+        <v>46583</v>
+      </c>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -8555,7 +9368,9 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A336" s="13"/>
+      <c r="A336" s="13">
+        <v>46584</v>
+      </c>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -8577,7 +9392,9 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A337" s="13"/>
+      <c r="A337" s="13">
+        <v>46585</v>
+      </c>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -8599,7 +9416,9 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A338" s="13"/>
+      <c r="A338" s="13">
+        <v>46586</v>
+      </c>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -8621,7 +9440,9 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A339" s="13"/>
+      <c r="A339" s="13">
+        <v>46587</v>
+      </c>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -8643,7 +9464,9 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A340" s="13"/>
+      <c r="A340" s="13">
+        <v>46588</v>
+      </c>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -8665,7 +9488,9 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A341" s="13"/>
+      <c r="A341" s="13">
+        <v>46589</v>
+      </c>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -8687,7 +9512,9 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A342" s="13"/>
+      <c r="A342" s="13">
+        <v>46590</v>
+      </c>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -8709,7 +9536,9 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A343" s="13"/>
+      <c r="A343" s="13">
+        <v>46591</v>
+      </c>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -8731,7 +9560,9 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A344" s="13"/>
+      <c r="A344" s="13">
+        <v>46592</v>
+      </c>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -8753,7 +9584,9 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A345" s="13"/>
+      <c r="A345" s="13">
+        <v>46593</v>
+      </c>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -8775,7 +9608,9 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A346" s="13"/>
+      <c r="A346" s="13">
+        <v>46594</v>
+      </c>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -8797,7 +9632,9 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A347" s="13"/>
+      <c r="A347" s="13">
+        <v>46595</v>
+      </c>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -8819,7 +9656,9 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A348" s="13"/>
+      <c r="A348" s="13">
+        <v>46596</v>
+      </c>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -8841,7 +9680,9 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A349" s="13"/>
+      <c r="A349" s="13">
+        <v>46597</v>
+      </c>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -8863,7 +9704,9 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A350" s="13"/>
+      <c r="A350" s="13">
+        <v>46598</v>
+      </c>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -8885,7 +9728,9 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A351" s="13"/>
+      <c r="A351" s="13">
+        <v>46599</v>
+      </c>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -8907,7 +9752,9 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A352" s="13"/>
+      <c r="A352" s="13">
+        <v>46600</v>
+      </c>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -8929,7 +9776,9 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A353" s="13"/>
+      <c r="A353" s="13">
+        <v>46601</v>
+      </c>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -8951,7 +9800,9 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A354" s="13"/>
+      <c r="A354" s="13">
+        <v>46602</v>
+      </c>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -8973,7 +9824,9 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A355" s="13"/>
+      <c r="A355" s="13">
+        <v>46603</v>
+      </c>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -8995,7 +9848,9 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A356" s="13"/>
+      <c r="A356" s="13">
+        <v>46604</v>
+      </c>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -9017,7 +9872,9 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A357" s="13"/>
+      <c r="A357" s="13">
+        <v>46605</v>
+      </c>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -9039,7 +9896,9 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A358" s="13"/>
+      <c r="A358" s="13">
+        <v>46606</v>
+      </c>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -9061,7 +9920,9 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A359" s="13"/>
+      <c r="A359" s="13">
+        <v>46607</v>
+      </c>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -9083,7 +9944,9 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A360" s="13"/>
+      <c r="A360" s="13">
+        <v>46608</v>
+      </c>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -9105,7 +9968,9 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A361" s="13"/>
+      <c r="A361" s="13">
+        <v>46609</v>
+      </c>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -9127,7 +9992,9 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A362" s="13"/>
+      <c r="A362" s="13">
+        <v>46610</v>
+      </c>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -9149,7 +10016,9 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A363" s="13"/>
+      <c r="A363" s="13">
+        <v>46611</v>
+      </c>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -9171,7 +10040,9 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A364" s="13"/>
+      <c r="A364" s="13">
+        <v>46612</v>
+      </c>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -9193,7 +10064,9 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A365" s="13"/>
+      <c r="A365" s="13">
+        <v>46613</v>
+      </c>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -9215,7 +10088,9 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A366" s="13"/>
+      <c r="A366" s="13">
+        <v>46614</v>
+      </c>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -9237,7 +10112,9 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A367" s="13"/>
+      <c r="A367" s="13">
+        <v>46615</v>
+      </c>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -9259,7 +10136,9 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A368" s="13"/>
+      <c r="A368" s="13">
+        <v>46616</v>
+      </c>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -9281,7 +10160,9 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A369" s="13"/>
+      <c r="A369" s="13">
+        <v>46617</v>
+      </c>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -9303,7 +10184,9 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A370" s="13"/>
+      <c r="A370" s="13">
+        <v>46618</v>
+      </c>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -9325,7 +10208,9 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A371" s="13"/>
+      <c r="A371" s="13">
+        <v>46619</v>
+      </c>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -9347,7 +10232,9 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A372" s="13"/>
+      <c r="A372" s="13">
+        <v>46620</v>
+      </c>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -9369,7 +10256,9 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A373" s="13"/>
+      <c r="A373" s="13">
+        <v>46621</v>
+      </c>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -9391,7 +10280,9 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A374" s="13"/>
+      <c r="A374" s="13">
+        <v>46622</v>
+      </c>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -9413,7 +10304,9 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A375" s="13"/>
+      <c r="A375" s="13">
+        <v>46623</v>
+      </c>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -9435,7 +10328,9 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A376" s="13"/>
+      <c r="A376" s="13">
+        <v>46624</v>
+      </c>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -9457,7 +10352,9 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A377" s="13"/>
+      <c r="A377" s="13">
+        <v>46625</v>
+      </c>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -9479,7 +10376,9 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A378" s="13"/>
+      <c r="A378" s="13">
+        <v>46626</v>
+      </c>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -9501,7 +10400,9 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A379" s="13"/>
+      <c r="A379" s="13">
+        <v>46627</v>
+      </c>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -9523,7 +10424,9 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A380" s="13"/>
+      <c r="A380" s="13">
+        <v>46628</v>
+      </c>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -9545,7 +10448,9 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A381" s="13"/>
+      <c r="A381" s="13">
+        <v>46629</v>
+      </c>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -9567,7 +10472,9 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A382" s="13"/>
+      <c r="A382" s="13">
+        <v>46630</v>
+      </c>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -9589,7 +10496,9 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A383" s="13"/>
+      <c r="A383" s="13">
+        <v>46631</v>
+      </c>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -9611,7 +10520,9 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A384" s="13"/>
+      <c r="A384" s="13">
+        <v>46632</v>
+      </c>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -9633,7 +10544,9 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A385" s="13"/>
+      <c r="A385" s="13">
+        <v>46633</v>
+      </c>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -9655,7 +10568,9 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A386" s="13"/>
+      <c r="A386" s="13">
+        <v>46634</v>
+      </c>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -9677,7 +10592,9 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A387" s="13"/>
+      <c r="A387" s="13">
+        <v>46635</v>
+      </c>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -9699,7 +10616,9 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A388" s="13"/>
+      <c r="A388" s="13">
+        <v>46636</v>
+      </c>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -9721,7 +10640,9 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A389" s="13"/>
+      <c r="A389" s="13">
+        <v>46637</v>
+      </c>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -9743,7 +10664,9 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A390" s="13"/>
+      <c r="A390" s="13">
+        <v>46638</v>
+      </c>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -9765,7 +10688,9 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A391" s="13"/>
+      <c r="A391" s="13">
+        <v>46639</v>
+      </c>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -9787,7 +10712,9 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A392" s="13"/>
+      <c r="A392" s="13">
+        <v>46640</v>
+      </c>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -9809,7 +10736,9 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A393" s="13"/>
+      <c r="A393" s="13">
+        <v>46641</v>
+      </c>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -9831,7 +10760,9 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A394" s="13"/>
+      <c r="A394" s="13">
+        <v>46642</v>
+      </c>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -9853,7 +10784,9 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A395" s="13"/>
+      <c r="A395" s="13">
+        <v>46643</v>
+      </c>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -9875,7 +10808,9 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A396" s="13"/>
+      <c r="A396" s="13">
+        <v>46644</v>
+      </c>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -9897,7 +10832,9 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A397" s="13"/>
+      <c r="A397" s="13">
+        <v>46645</v>
+      </c>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -9919,7 +10856,9 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A398" s="13"/>
+      <c r="A398" s="13">
+        <v>46646</v>
+      </c>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -9941,7 +10880,9 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A399" s="13"/>
+      <c r="A399" s="13">
+        <v>46647</v>
+      </c>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -9963,7 +10904,9 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A400" s="13"/>
+      <c r="A400" s="13">
+        <v>46648</v>
+      </c>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -9985,7 +10928,9 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A401" s="13"/>
+      <c r="A401" s="13">
+        <v>46649</v>
+      </c>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/PYTHON/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8130E1EF-ACFB-4C40-BDBD-F3BDF079432F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6426953A-5A6A-475C-87EA-2D214B84B9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>Distrubed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Exprience </t>
+  </si>
+  <si>
+    <t>Experience</t>
   </si>
 </sst>
 </file>
@@ -1116,25 +1122,31 @@
       <c r="B7" s="14">
         <v>420</v>
       </c>
-      <c r="C7" s="14"/>
+      <c r="C7" s="14">
+        <v>25</v>
+      </c>
       <c r="D7" s="14">
         <v>200</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="14">
+        <v>45</v>
+      </c>
       <c r="F7" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="G7" s="14">
-        <v>4</v>
-      </c>
-      <c r="H7" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>30</v>
+      </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>540</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1154,12 +1166,14 @@
       <c r="B8" s="14">
         <v>420</v>
       </c>
-      <c r="C8" s="14"/>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
       <c r="D8" s="14">
         <v>300</v>
       </c>
       <c r="E8" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F8" s="14">
         <v>0</v>
@@ -1167,14 +1181,16 @@
       <c r="G8" s="14">
         <v>0</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>540</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>59</v>
@@ -1194,21 +1210,31 @@
       <c r="B9" s="14">
         <v>420</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
       <c r="D9" s="14">
         <v>240</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>900</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>540</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>59</v>
@@ -1228,7 +1254,9 @@
       <c r="B10" s="14">
         <v>480</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
       <c r="D10" s="14">
         <v>200</v>
       </c>
@@ -1236,19 +1264,21 @@
         <v>40</v>
       </c>
       <c r="F10" s="14">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="G10" s="14">
-        <v>7</v>
-      </c>
-      <c r="H10" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>35</v>
+      </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1025</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1268,7 +1298,9 @@
       <c r="B11" s="14">
         <v>480</v>
       </c>
-      <c r="C11" s="14"/>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
       <c r="D11" s="14">
         <v>210</v>
       </c>
@@ -1276,19 +1308,21 @@
         <v>40</v>
       </c>
       <c r="F11" s="14">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="G11" s="14">
         <v>7</v>
       </c>
-      <c r="H11" s="14"/>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
@@ -1302,7 +1336,9 @@
       <c r="B12" s="14">
         <v>480</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="14">
+        <v>25</v>
+      </c>
       <c r="D12" s="14">
         <v>210</v>
       </c>
@@ -1310,19 +1346,21 @@
         <v>40</v>
       </c>
       <c r="F12" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="G12" s="14">
-        <v>5</v>
-      </c>
-      <c r="H12" s="14"/>
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>30</v>
+      </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1205</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>235</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>57</v>
@@ -1344,9 +1382,11 @@
       <c r="B13" s="14">
         <v>480</v>
       </c>
-      <c r="C13" s="14"/>
+      <c r="C13" s="14">
+        <v>32</v>
+      </c>
       <c r="D13" s="14">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="E13" s="14">
         <v>40</v>
@@ -1357,14 +1397,16 @@
       <c r="G13" s="14">
         <v>4</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="14">
+        <v>40</v>
+      </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1012</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1384,7 +1426,9 @@
       <c r="B14" s="14">
         <v>480</v>
       </c>
-      <c r="C14" s="14"/>
+      <c r="C14" s="14">
+        <v>25</v>
+      </c>
       <c r="D14" s="14">
         <v>210</v>
       </c>
@@ -1397,14 +1441,16 @@
       <c r="G14" s="14">
         <v>3</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="14">
+        <v>35</v>
+      </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>970</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>470</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>61</v>
@@ -1420,7 +1466,9 @@
         <v>46263</v>
       </c>
       <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+      <c r="C15" s="14">
+        <v>45</v>
+      </c>
       <c r="D15" s="14">
         <v>300</v>
       </c>
@@ -1433,14 +1481,16 @@
       <c r="G15" s="14">
         <v>0</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="14">
+        <v>90</v>
+      </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>340</v>
+        <v>475</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>965</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1460,7 +1510,9 @@
       <c r="B16" s="14">
         <v>480</v>
       </c>
-      <c r="C16" s="14"/>
+      <c r="C16" s="14">
+        <v>50</v>
+      </c>
       <c r="D16" s="14">
         <v>410</v>
       </c>
@@ -1473,14 +1525,16 @@
       <c r="G16" s="14">
         <v>0</v>
       </c>
-      <c r="H16" s="14"/>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>1110</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>61</v>
@@ -1502,7 +1556,9 @@
       <c r="B17" s="14">
         <v>480</v>
       </c>
-      <c r="C17" s="14"/>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
       <c r="D17" s="14">
         <v>275</v>
       </c>
@@ -1515,14 +1571,16 @@
       <c r="G17" s="14">
         <v>4</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="14">
+        <v>40</v>
+      </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1055</v>
+        <v>1125</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>61</v>
@@ -1544,7 +1602,9 @@
       <c r="B18" s="14">
         <v>480</v>
       </c>
-      <c r="C18" s="14"/>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
       <c r="D18" s="14">
         <v>180</v>
       </c>
@@ -1557,14 +1617,16 @@
       <c r="G18" s="14">
         <v>7</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1190</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>57</v>
@@ -1586,7 +1648,9 @@
       <c r="B19" s="14">
         <v>300</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="14">
+        <v>25</v>
+      </c>
       <c r="D19" s="14">
         <v>200</v>
       </c>
@@ -1599,14 +1663,16 @@
       <c r="G19" s="14">
         <v>7</v>
       </c>
-      <c r="H19" s="14"/>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>975</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1628,7 +1694,9 @@
       <c r="B20" s="14">
         <v>480</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
       <c r="D20" s="14">
         <v>210</v>
       </c>
@@ -1641,14 +1709,16 @@
       <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="H20" s="14"/>
+      <c r="H20" s="14">
+        <v>35</v>
+      </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1045</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>395</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>61</v>
@@ -1670,7 +1740,9 @@
       <c r="B21" s="14">
         <v>480</v>
       </c>
-      <c r="C21" s="14"/>
+      <c r="C21" s="14">
+        <v>35</v>
+      </c>
       <c r="D21" s="14">
         <v>195</v>
       </c>
@@ -1683,14 +1755,16 @@
       <c r="G21" s="14">
         <v>5</v>
       </c>
-      <c r="H21" s="14"/>
+      <c r="H21" s="14">
+        <v>20</v>
+      </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1035</v>
+        <v>1090</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>405</v>
+        <v>350</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>
@@ -1712,7 +1786,9 @@
       <c r="B22" s="14">
         <v>420</v>
       </c>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14">
+        <v>40</v>
+      </c>
       <c r="D22" s="14">
         <v>420</v>
       </c>
@@ -1725,14 +1801,16 @@
       <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="14">
+        <v>90</v>
+      </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>1060</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>380</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
@@ -1754,7 +1832,9 @@
       <c r="B23" s="14">
         <v>420</v>
       </c>
-      <c r="C23" s="14"/>
+      <c r="C23" s="14">
+        <v>50</v>
+      </c>
       <c r="D23" s="14">
         <v>315</v>
       </c>
@@ -1767,14 +1847,16 @@
       <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="14"/>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>935</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>505</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1796,7 +1878,9 @@
       <c r="B24" s="14">
         <v>480</v>
       </c>
-      <c r="C24" s="14"/>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
       <c r="D24" s="14">
         <v>120</v>
       </c>
@@ -1809,14 +1893,16 @@
       <c r="G24" s="14">
         <v>4</v>
       </c>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>61</v>
@@ -1838,7 +1924,9 @@
       <c r="B25" s="14">
         <v>420</v>
       </c>
-      <c r="C25" s="14"/>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
       <c r="D25" s="14">
         <v>150</v>
       </c>
@@ -1851,7 +1939,9 @@
       <c r="G25" s="14">
         <v>7</v>
       </c>
-      <c r="H25" s="14"/>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
         <v>1030</v>
@@ -1880,7 +1970,9 @@
       <c r="B26" s="14">
         <v>300</v>
       </c>
-      <c r="C26" s="14"/>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
       <c r="D26" s="14">
         <v>205</v>
       </c>
@@ -1893,7 +1985,9 @@
       <c r="G26" s="14">
         <v>2</v>
       </c>
-      <c r="H26" s="14"/>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
         <v>625</v>
@@ -1922,7 +2016,9 @@
       <c r="B27" s="14">
         <v>480</v>
       </c>
-      <c r="C27" s="14"/>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
       <c r="D27" s="14">
         <v>120</v>
       </c>
@@ -1935,7 +2031,9 @@
       <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="H27" s="14"/>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
         <v>870</v>
@@ -1964,7 +2062,9 @@
       <c r="B28" s="14">
         <v>420</v>
       </c>
-      <c r="C28" s="14"/>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
       <c r="D28" s="14">
         <v>0</v>
       </c>
@@ -1977,7 +2077,9 @@
       <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="H28" s="14"/>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
         <v>600</v>
@@ -2003,121 +2105,231 @@
       <c r="A29" s="13">
         <v>46277</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>540</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
         <v>46278</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>25</v>
+      </c>
+      <c r="D30" s="14">
+        <v>305</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>35</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
         <v>46279</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>360</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>240</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>30</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
         <v>46280</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="B32" s="14">
+        <v>300</v>
+      </c>
+      <c r="C32" s="14">
+        <v>25</v>
+      </c>
+      <c r="D32" s="14">
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>420</v>
+      </c>
+      <c r="G32" s="14">
+        <v>7</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>745</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>695</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
         <v>46281</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>360</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>360</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>40</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6426953A-5A6A-475C-87EA-2D214B84B9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FEBAC0-FF83-494C-A67C-F7FC3C2BCB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>Experience</t>
+  </si>
+  <si>
+    <t>o</t>
   </si>
 </sst>
 </file>
@@ -2335,78 +2338,142 @@
       <c r="A34" s="13">
         <v>46282</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>300</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>280</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>30</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
         <v>46283</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>360</v>
+      </c>
+      <c r="E35" s="14">
+        <v>40</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>25</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
         <v>46284</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>25</v>
+      </c>
+      <c r="D36" s="14">
+        <v>300</v>
+      </c>
+      <c r="E36" s="14">
+        <v>65</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13">
-        <v>46285</v>
-      </c>
+      <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2428,9 +2495,7 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13">
-        <v>46286</v>
-      </c>
+      <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2452,9 +2517,7 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13">
-        <v>46287</v>
-      </c>
+      <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2476,9 +2539,7 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13">
-        <v>46288</v>
-      </c>
+      <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -2500,9 +2561,7 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13">
-        <v>46289</v>
-      </c>
+      <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2524,9 +2583,7 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13">
-        <v>46290</v>
-      </c>
+      <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -2548,9 +2605,7 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13">
-        <v>46291</v>
-      </c>
+      <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2572,9 +2627,7 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13">
-        <v>46292</v>
-      </c>
+      <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -2596,9 +2649,7 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13">
-        <v>46293</v>
-      </c>
+      <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -2620,9 +2671,7 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13">
-        <v>46294</v>
-      </c>
+      <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2644,9 +2693,7 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13">
-        <v>46295</v>
-      </c>
+      <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2668,9 +2715,7 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13">
-        <v>46296</v>
-      </c>
+      <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2692,9 +2737,7 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13">
-        <v>46297</v>
-      </c>
+      <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2716,9 +2759,7 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13">
-        <v>46298</v>
-      </c>
+      <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2740,9 +2781,7 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13">
-        <v>46299</v>
-      </c>
+      <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2764,9 +2803,7 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13">
-        <v>46300</v>
-      </c>
+      <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2788,9 +2825,7 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13">
-        <v>46301</v>
-      </c>
+      <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2812,9 +2847,7 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13">
-        <v>46302</v>
-      </c>
+      <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2836,9 +2869,7 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13">
-        <v>46303</v>
-      </c>
+      <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2860,9 +2891,7 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13">
-        <v>46304</v>
-      </c>
+      <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -2884,9 +2913,7 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13">
-        <v>46305</v>
-      </c>
+      <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2908,9 +2935,7 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13">
-        <v>46306</v>
-      </c>
+      <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2932,9 +2957,7 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13">
-        <v>46307</v>
-      </c>
+      <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2956,9 +2979,7 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13">
-        <v>46308</v>
-      </c>
+      <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -2980,9 +3001,7 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13">
-        <v>46309</v>
-      </c>
+      <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -3004,9 +3023,7 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13">
-        <v>46310</v>
-      </c>
+      <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -3028,9 +3045,7 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13">
-        <v>46311</v>
-      </c>
+      <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3052,9 +3067,7 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13">
-        <v>46312</v>
-      </c>
+      <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3076,9 +3089,7 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13">
-        <v>46313</v>
-      </c>
+      <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3100,9 +3111,7 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13">
-        <v>46314</v>
-      </c>
+      <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3124,9 +3133,7 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13">
-        <v>46315</v>
-      </c>
+      <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3148,9 +3155,7 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13">
-        <v>46316</v>
-      </c>
+      <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3172,9 +3177,7 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13">
-        <v>46317</v>
-      </c>
+      <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3196,9 +3199,7 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13">
-        <v>46318</v>
-      </c>
+      <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3220,9 +3221,7 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13">
-        <v>46319</v>
-      </c>
+      <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3244,9 +3243,7 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13">
-        <v>46320</v>
-      </c>
+      <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3268,9 +3265,7 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13">
-        <v>46321</v>
-      </c>
+      <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3292,9 +3287,7 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13">
-        <v>46322</v>
-      </c>
+      <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3316,9 +3309,7 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13">
-        <v>46323</v>
-      </c>
+      <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3340,9 +3331,7 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13">
-        <v>46324</v>
-      </c>
+      <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3364,9 +3353,7 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13">
-        <v>46325</v>
-      </c>
+      <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3388,9 +3375,7 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13">
-        <v>46326</v>
-      </c>
+      <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3412,9 +3397,7 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="13">
-        <v>46327</v>
-      </c>
+      <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -3436,9 +3419,7 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="13">
-        <v>46328</v>
-      </c>
+      <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -3460,9 +3441,7 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13">
-        <v>46329</v>
-      </c>
+      <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -3484,9 +3463,7 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="13">
-        <v>46330</v>
-      </c>
+      <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -3508,9 +3485,7 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="13">
-        <v>46331</v>
-      </c>
+      <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -3532,9 +3507,7 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="13">
-        <v>46332</v>
-      </c>
+      <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -3556,9 +3529,7 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="13">
-        <v>46333</v>
-      </c>
+      <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -3580,9 +3551,7 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" s="13">
-        <v>46334</v>
-      </c>
+      <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -3604,9 +3573,7 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A87" s="13">
-        <v>46335</v>
-      </c>
+      <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -3628,9 +3595,7 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A88" s="13">
-        <v>46336</v>
-      </c>
+      <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3652,9 +3617,7 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A89" s="13">
-        <v>46337</v>
-      </c>
+      <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -3676,9 +3639,7 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A90" s="13">
-        <v>46338</v>
-      </c>
+      <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -3700,9 +3661,7 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A91" s="13">
-        <v>46339</v>
-      </c>
+      <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -3724,9 +3683,7 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A92" s="13">
-        <v>46340</v>
-      </c>
+      <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -3748,9 +3705,7 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A93" s="13">
-        <v>46341</v>
-      </c>
+      <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -3772,9 +3727,7 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A94" s="13">
-        <v>46342</v>
-      </c>
+      <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -3796,9 +3749,7 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A95" s="13">
-        <v>46343</v>
-      </c>
+      <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -3820,9 +3771,7 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A96" s="13">
-        <v>46344</v>
-      </c>
+      <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -3844,9 +3793,7 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A97" s="13">
-        <v>46345</v>
-      </c>
+      <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -3868,9 +3815,7 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A98" s="13">
-        <v>46346</v>
-      </c>
+      <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -3892,9 +3837,7 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A99" s="13">
-        <v>46347</v>
-      </c>
+      <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -3916,9 +3859,7 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A100" s="13">
-        <v>46348</v>
-      </c>
+      <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -3940,9 +3881,7 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A101" s="13">
-        <v>46349</v>
-      </c>
+      <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -3964,9 +3903,7 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A102" s="13">
-        <v>46350</v>
-      </c>
+      <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -3988,9 +3925,7 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A103" s="13">
-        <v>46351</v>
-      </c>
+      <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -4012,9 +3947,7 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A104" s="13">
-        <v>46352</v>
-      </c>
+      <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -4036,9 +3969,7 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A105" s="13">
-        <v>46353</v>
-      </c>
+      <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -4060,9 +3991,7 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A106" s="13">
-        <v>46354</v>
-      </c>
+      <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -4084,9 +4013,7 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A107" s="13">
-        <v>46355</v>
-      </c>
+      <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -4108,9 +4035,7 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A108" s="13">
-        <v>46356</v>
-      </c>
+      <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -4132,9 +4057,7 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A109" s="13">
-        <v>46357</v>
-      </c>
+      <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -4156,9 +4079,7 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A110" s="13">
-        <v>46358</v>
-      </c>
+      <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -4180,9 +4101,7 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A111" s="13">
-        <v>46359</v>
-      </c>
+      <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -4204,9 +4123,7 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A112" s="13">
-        <v>46360</v>
-      </c>
+      <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -4228,9 +4145,7 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="13">
-        <v>46361</v>
-      </c>
+      <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -4252,9 +4167,7 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="13">
-        <v>46362</v>
-      </c>
+      <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -4276,9 +4189,7 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="13">
-        <v>46363</v>
-      </c>
+      <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -4300,9 +4211,7 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="13">
-        <v>46364</v>
-      </c>
+      <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -4324,9 +4233,7 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="13">
-        <v>46365</v>
-      </c>
+      <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -4348,9 +4255,7 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A118" s="13">
-        <v>46366</v>
-      </c>
+      <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -4372,9 +4277,7 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A119" s="13">
-        <v>46367</v>
-      </c>
+      <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -4396,9 +4299,7 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A120" s="13">
-        <v>46368</v>
-      </c>
+      <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -4420,9 +4321,7 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="13">
-        <v>46369</v>
-      </c>
+      <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -4444,9 +4343,7 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A122" s="13">
-        <v>46370</v>
-      </c>
+      <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -4468,9 +4365,7 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A123" s="13">
-        <v>46371</v>
-      </c>
+      <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -4492,9 +4387,7 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A124" s="13">
-        <v>46372</v>
-      </c>
+      <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -4516,9 +4409,7 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A125" s="13">
-        <v>46373</v>
-      </c>
+      <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -4540,9 +4431,7 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A126" s="13">
-        <v>46374</v>
-      </c>
+      <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -4564,9 +4453,7 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A127" s="13">
-        <v>46375</v>
-      </c>
+      <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -4588,9 +4475,7 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="13">
-        <v>46376</v>
-      </c>
+      <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4612,9 +4497,7 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A129" s="13">
-        <v>46377</v>
-      </c>
+      <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4636,9 +4519,7 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A130" s="13">
-        <v>46378</v>
-      </c>
+      <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4660,9 +4541,7 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A131" s="13">
-        <v>46379</v>
-      </c>
+      <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -4684,9 +4563,7 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A132" s="13">
-        <v>46380</v>
-      </c>
+      <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -4708,9 +4585,7 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A133" s="13">
-        <v>46381</v>
-      </c>
+      <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -4732,9 +4607,7 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A134" s="13">
-        <v>46382</v>
-      </c>
+      <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -4756,9 +4629,7 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A135" s="13">
-        <v>46383</v>
-      </c>
+      <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -4780,9 +4651,7 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A136" s="13">
-        <v>46384</v>
-      </c>
+      <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -4804,9 +4673,7 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A137" s="13">
-        <v>46385</v>
-      </c>
+      <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -4828,9 +4695,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A138" s="13">
-        <v>46386</v>
-      </c>
+      <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -4852,9 +4717,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A139" s="13">
-        <v>46387</v>
-      </c>
+      <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -4876,9 +4739,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A140" s="13">
-        <v>46388</v>
-      </c>
+      <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -4900,9 +4761,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A141" s="13">
-        <v>46389</v>
-      </c>
+      <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4924,9 +4783,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A142" s="13">
-        <v>46390</v>
-      </c>
+      <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4948,9 +4805,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A143" s="13">
-        <v>46391</v>
-      </c>
+      <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4972,9 +4827,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A144" s="13">
-        <v>46392</v>
-      </c>
+      <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4996,9 +4849,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A145" s="13">
-        <v>46393</v>
-      </c>
+      <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -5020,9 +4871,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A146" s="13">
-        <v>46394</v>
-      </c>
+      <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -5044,9 +4893,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A147" s="13">
-        <v>46395</v>
-      </c>
+      <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -5068,9 +4915,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A148" s="13">
-        <v>46396</v>
-      </c>
+      <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -5092,9 +4937,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A149" s="13">
-        <v>46397</v>
-      </c>
+      <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -5116,9 +4959,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A150" s="13">
-        <v>46398</v>
-      </c>
+      <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -5140,9 +4981,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A151" s="13">
-        <v>46399</v>
-      </c>
+      <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -5164,9 +5003,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A152" s="13">
-        <v>46400</v>
-      </c>
+      <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -5188,9 +5025,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A153" s="13">
-        <v>46401</v>
-      </c>
+      <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -5212,9 +5047,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A154" s="13">
-        <v>46402</v>
-      </c>
+      <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -5236,9 +5069,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A155" s="13">
-        <v>46403</v>
-      </c>
+      <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -5260,9 +5091,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A156" s="13">
-        <v>46404</v>
-      </c>
+      <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -5284,9 +5113,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A157" s="13">
-        <v>46405</v>
-      </c>
+      <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -5308,9 +5135,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A158" s="13">
-        <v>46406</v>
-      </c>
+      <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -5332,9 +5157,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A159" s="13">
-        <v>46407</v>
-      </c>
+      <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -5356,9 +5179,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A160" s="13">
-        <v>46408</v>
-      </c>
+      <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -5380,9 +5201,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A161" s="13">
-        <v>46409</v>
-      </c>
+      <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -5404,9 +5223,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A162" s="13">
-        <v>46410</v>
-      </c>
+      <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -5428,9 +5245,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A163" s="13">
-        <v>46411</v>
-      </c>
+      <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -5452,9 +5267,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A164" s="13">
-        <v>46412</v>
-      </c>
+      <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -5476,9 +5289,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A165" s="13">
-        <v>46413</v>
-      </c>
+      <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -5500,9 +5311,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A166" s="13">
-        <v>46414</v>
-      </c>
+      <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -5524,9 +5333,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A167" s="13">
-        <v>46415</v>
-      </c>
+      <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -5548,9 +5355,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A168" s="13">
-        <v>46416</v>
-      </c>
+      <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -5572,9 +5377,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A169" s="13">
-        <v>46417</v>
-      </c>
+      <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -5596,9 +5399,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A170" s="13">
-        <v>46418</v>
-      </c>
+      <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -5620,9 +5421,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A171" s="13">
-        <v>46419</v>
-      </c>
+      <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -5644,9 +5443,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A172" s="13">
-        <v>46420</v>
-      </c>
+      <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -5668,9 +5465,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A173" s="13">
-        <v>46421</v>
-      </c>
+      <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -5692,9 +5487,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A174" s="13">
-        <v>46422</v>
-      </c>
+      <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5716,9 +5509,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A175" s="13">
-        <v>46423</v>
-      </c>
+      <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5740,9 +5531,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A176" s="13">
-        <v>46424</v>
-      </c>
+      <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5764,9 +5553,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A177" s="13">
-        <v>46425</v>
-      </c>
+      <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -5788,9 +5575,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A178" s="13">
-        <v>46426</v>
-      </c>
+      <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -5812,9 +5597,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A179" s="13">
-        <v>46427</v>
-      </c>
+      <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -5836,9 +5619,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A180" s="13">
-        <v>46428</v>
-      </c>
+      <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -5860,9 +5641,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A181" s="13">
-        <v>46429</v>
-      </c>
+      <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -5884,9 +5663,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A182" s="13">
-        <v>46430</v>
-      </c>
+      <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -5908,9 +5685,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A183" s="13">
-        <v>46431</v>
-      </c>
+      <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -5932,9 +5707,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A184" s="13">
-        <v>46432</v>
-      </c>
+      <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5956,9 +5729,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A185" s="13">
-        <v>46433</v>
-      </c>
+      <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5980,9 +5751,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A186" s="13">
-        <v>46434</v>
-      </c>
+      <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -6004,9 +5773,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A187" s="13">
-        <v>46435</v>
-      </c>
+      <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -6028,9 +5795,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A188" s="13">
-        <v>46436</v>
-      </c>
+      <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -6052,9 +5817,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A189" s="13">
-        <v>46437</v>
-      </c>
+      <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -6076,9 +5839,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A190" s="13">
-        <v>46438</v>
-      </c>
+      <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -6100,9 +5861,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A191" s="13">
-        <v>46439</v>
-      </c>
+      <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -6124,9 +5883,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A192" s="13">
-        <v>46440</v>
-      </c>
+      <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -6148,9 +5905,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A193" s="13">
-        <v>46441</v>
-      </c>
+      <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -6172,9 +5927,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A194" s="13">
-        <v>46442</v>
-      </c>
+      <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -6196,9 +5949,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A195" s="13">
-        <v>46443</v>
-      </c>
+      <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -6220,9 +5971,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A196" s="13">
-        <v>46444</v>
-      </c>
+      <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -6244,9 +5993,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A197" s="13">
-        <v>46445</v>
-      </c>
+      <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -6268,9 +6015,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A198" s="13">
-        <v>46446</v>
-      </c>
+      <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -6292,9 +6037,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A199" s="13">
-        <v>46447</v>
-      </c>
+      <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -6316,9 +6059,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A200" s="13">
-        <v>46448</v>
-      </c>
+      <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -6340,9 +6081,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A201" s="13">
-        <v>46449</v>
-      </c>
+      <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -6364,9 +6103,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A202" s="13">
-        <v>46450</v>
-      </c>
+      <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -6388,9 +6125,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A203" s="13">
-        <v>46451</v>
-      </c>
+      <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -6412,9 +6147,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A204" s="13">
-        <v>46452</v>
-      </c>
+      <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -6436,9 +6169,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A205" s="13">
-        <v>46453</v>
-      </c>
+      <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -6460,9 +6191,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A206" s="13">
-        <v>46454</v>
-      </c>
+      <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -6484,9 +6213,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A207" s="13">
-        <v>46455</v>
-      </c>
+      <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -6508,9 +6235,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A208" s="13">
-        <v>46456</v>
-      </c>
+      <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -6532,9 +6257,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A209" s="13">
-        <v>46457</v>
-      </c>
+      <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -6556,9 +6279,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A210" s="13">
-        <v>46458</v>
-      </c>
+      <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -6580,9 +6301,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A211" s="13">
-        <v>46459</v>
-      </c>
+      <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -6604,9 +6323,7 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A212" s="13">
-        <v>46460</v>
-      </c>
+      <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -6628,9 +6345,7 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A213" s="13">
-        <v>46461</v>
-      </c>
+      <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -6652,9 +6367,7 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A214" s="13">
-        <v>46462</v>
-      </c>
+      <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -6676,9 +6389,7 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A215" s="13">
-        <v>46463</v>
-      </c>
+      <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -6700,9 +6411,7 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A216" s="13">
-        <v>46464</v>
-      </c>
+      <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -6724,9 +6433,7 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A217" s="13">
-        <v>46465</v>
-      </c>
+      <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -6748,9 +6455,7 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A218" s="13">
-        <v>46466</v>
-      </c>
+      <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -6772,9 +6477,7 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A219" s="13">
-        <v>46467</v>
-      </c>
+      <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -6796,9 +6499,7 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A220" s="13">
-        <v>46468</v>
-      </c>
+      <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -6820,9 +6521,7 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A221" s="13">
-        <v>46469</v>
-      </c>
+      <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -6844,9 +6543,7 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A222" s="13">
-        <v>46470</v>
-      </c>
+      <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -6868,9 +6565,7 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A223" s="13">
-        <v>46471</v>
-      </c>
+      <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -6892,9 +6587,7 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A224" s="13">
-        <v>46472</v>
-      </c>
+      <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -6916,9 +6609,7 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A225" s="13">
-        <v>46473</v>
-      </c>
+      <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -6940,9 +6631,7 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A226" s="13">
-        <v>46474</v>
-      </c>
+      <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -6964,9 +6653,7 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A227" s="13">
-        <v>46475</v>
-      </c>
+      <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -6988,9 +6675,7 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A228" s="13">
-        <v>46476</v>
-      </c>
+      <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -7012,9 +6697,7 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A229" s="13">
-        <v>46477</v>
-      </c>
+      <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -7036,9 +6719,7 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A230" s="13">
-        <v>46478</v>
-      </c>
+      <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -7060,9 +6741,7 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A231" s="13">
-        <v>46479</v>
-      </c>
+      <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -7084,9 +6763,7 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A232" s="13">
-        <v>46480</v>
-      </c>
+      <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -7108,9 +6785,7 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A233" s="13">
-        <v>46481</v>
-      </c>
+      <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -7132,9 +6807,7 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A234" s="13">
-        <v>46482</v>
-      </c>
+      <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -7156,9 +6829,7 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A235" s="13">
-        <v>46483</v>
-      </c>
+      <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -7180,9 +6851,7 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A236" s="13">
-        <v>46484</v>
-      </c>
+      <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -7204,9 +6873,7 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A237" s="13">
-        <v>46485</v>
-      </c>
+      <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -7228,9 +6895,7 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A238" s="13">
-        <v>46486</v>
-      </c>
+      <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -7252,9 +6917,7 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A239" s="13">
-        <v>46487</v>
-      </c>
+      <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -7276,9 +6939,7 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A240" s="13">
-        <v>46488</v>
-      </c>
+      <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -7300,9 +6961,7 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A241" s="13">
-        <v>46489</v>
-      </c>
+      <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -7324,9 +6983,7 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A242" s="13">
-        <v>46490</v>
-      </c>
+      <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -7348,9 +7005,7 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A243" s="13">
-        <v>46491</v>
-      </c>
+      <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -7372,9 +7027,7 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A244" s="13">
-        <v>46492</v>
-      </c>
+      <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -7396,9 +7049,7 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A245" s="13">
-        <v>46493</v>
-      </c>
+      <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -7420,9 +7071,7 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A246" s="13">
-        <v>46494</v>
-      </c>
+      <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -7444,9 +7093,7 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A247" s="13">
-        <v>46495</v>
-      </c>
+      <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -7468,9 +7115,7 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A248" s="13">
-        <v>46496</v>
-      </c>
+      <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -7492,9 +7137,7 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A249" s="13">
-        <v>46497</v>
-      </c>
+      <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -7516,9 +7159,7 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A250" s="13">
-        <v>46498</v>
-      </c>
+      <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -7540,9 +7181,7 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A251" s="13">
-        <v>46499</v>
-      </c>
+      <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -7564,9 +7203,7 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A252" s="13">
-        <v>46500</v>
-      </c>
+      <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -7588,9 +7225,7 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A253" s="13">
-        <v>46501</v>
-      </c>
+      <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -7612,9 +7247,7 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A254" s="13">
-        <v>46502</v>
-      </c>
+      <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -7636,9 +7269,7 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A255" s="13">
-        <v>46503</v>
-      </c>
+      <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -7660,9 +7291,7 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A256" s="13">
-        <v>46504</v>
-      </c>
+      <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -7684,9 +7313,7 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A257" s="13">
-        <v>46505</v>
-      </c>
+      <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -7708,9 +7335,7 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A258" s="13">
-        <v>46506</v>
-      </c>
+      <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -7732,9 +7357,7 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A259" s="13">
-        <v>46507</v>
-      </c>
+      <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -7756,9 +7379,7 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A260" s="13">
-        <v>46508</v>
-      </c>
+      <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -7780,9 +7401,7 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A261" s="13">
-        <v>46509</v>
-      </c>
+      <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -7804,9 +7423,7 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A262" s="13">
-        <v>46510</v>
-      </c>
+      <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -7828,9 +7445,7 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A263" s="13">
-        <v>46511</v>
-      </c>
+      <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -7852,9 +7467,7 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A264" s="13">
-        <v>46512</v>
-      </c>
+      <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -7876,9 +7489,7 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A265" s="13">
-        <v>46513</v>
-      </c>
+      <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -7900,9 +7511,7 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A266" s="13">
-        <v>46514</v>
-      </c>
+      <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -7924,9 +7533,7 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A267" s="13">
-        <v>46515</v>
-      </c>
+      <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -7948,9 +7555,7 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A268" s="13">
-        <v>46516</v>
-      </c>
+      <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -7972,9 +7577,7 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A269" s="13">
-        <v>46517</v>
-      </c>
+      <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -7996,9 +7599,7 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A270" s="13">
-        <v>46518</v>
-      </c>
+      <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -8020,9 +7621,7 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A271" s="13">
-        <v>46519</v>
-      </c>
+      <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -8044,9 +7643,7 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A272" s="13">
-        <v>46520</v>
-      </c>
+      <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -8068,9 +7665,7 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A273" s="13">
-        <v>46521</v>
-      </c>
+      <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -8092,9 +7687,7 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A274" s="13">
-        <v>46522</v>
-      </c>
+      <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -8116,9 +7709,7 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A275" s="13">
-        <v>46523</v>
-      </c>
+      <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -8140,9 +7731,7 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A276" s="13">
-        <v>46524</v>
-      </c>
+      <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -8164,9 +7753,7 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A277" s="13">
-        <v>46525</v>
-      </c>
+      <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -8188,9 +7775,7 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A278" s="13">
-        <v>46526</v>
-      </c>
+      <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -8212,9 +7797,7 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A279" s="13">
-        <v>46527</v>
-      </c>
+      <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -8236,9 +7819,7 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A280" s="13">
-        <v>46528</v>
-      </c>
+      <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -8260,9 +7841,7 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A281" s="13">
-        <v>46529</v>
-      </c>
+      <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -8284,9 +7863,7 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A282" s="13">
-        <v>46530</v>
-      </c>
+      <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -8308,9 +7885,7 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A283" s="13">
-        <v>46531</v>
-      </c>
+      <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -8332,9 +7907,7 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A284" s="13">
-        <v>46532</v>
-      </c>
+      <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -8356,9 +7929,7 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A285" s="13">
-        <v>46533</v>
-      </c>
+      <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -8380,9 +7951,7 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A286" s="13">
-        <v>46534</v>
-      </c>
+      <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -8404,9 +7973,7 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A287" s="13">
-        <v>46535</v>
-      </c>
+      <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -8428,9 +7995,7 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A288" s="13">
-        <v>46536</v>
-      </c>
+      <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -8452,9 +8017,7 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A289" s="13">
-        <v>46537</v>
-      </c>
+      <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -8476,9 +8039,7 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A290" s="13">
-        <v>46538</v>
-      </c>
+      <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -8500,9 +8061,7 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A291" s="13">
-        <v>46539</v>
-      </c>
+      <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -8524,9 +8083,7 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A292" s="13">
-        <v>46540</v>
-      </c>
+      <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -8548,9 +8105,7 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A293" s="13">
-        <v>46541</v>
-      </c>
+      <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -8572,9 +8127,7 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A294" s="13">
-        <v>46542</v>
-      </c>
+      <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -8596,9 +8149,7 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A295" s="13">
-        <v>46543</v>
-      </c>
+      <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -8620,9 +8171,7 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A296" s="13">
-        <v>46544</v>
-      </c>
+      <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -8644,9 +8193,7 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A297" s="13">
-        <v>46545</v>
-      </c>
+      <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -8668,9 +8215,7 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A298" s="13">
-        <v>46546</v>
-      </c>
+      <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -8692,9 +8237,7 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A299" s="13">
-        <v>46547</v>
-      </c>
+      <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -8716,9 +8259,7 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A300" s="13">
-        <v>46548</v>
-      </c>
+      <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -8740,9 +8281,7 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A301" s="13">
-        <v>46549</v>
-      </c>
+      <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -8764,9 +8303,7 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A302" s="13">
-        <v>46550</v>
-      </c>
+      <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -8788,9 +8325,7 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A303" s="13">
-        <v>46551</v>
-      </c>
+      <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -8812,9 +8347,7 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A304" s="13">
-        <v>46552</v>
-      </c>
+      <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -8836,9 +8369,7 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A305" s="13">
-        <v>46553</v>
-      </c>
+      <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -8860,9 +8391,7 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A306" s="13">
-        <v>46554</v>
-      </c>
+      <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -8884,9 +8413,7 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A307" s="13">
-        <v>46555</v>
-      </c>
+      <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -8908,9 +8435,7 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A308" s="13">
-        <v>46556</v>
-      </c>
+      <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -8932,9 +8457,7 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A309" s="13">
-        <v>46557</v>
-      </c>
+      <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -8956,9 +8479,7 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A310" s="13">
-        <v>46558</v>
-      </c>
+      <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -8980,9 +8501,7 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A311" s="13">
-        <v>46559</v>
-      </c>
+      <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -9004,9 +8523,7 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A312" s="13">
-        <v>46560</v>
-      </c>
+      <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -9028,9 +8545,7 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A313" s="13">
-        <v>46561</v>
-      </c>
+      <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -9052,9 +8567,7 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A314" s="13">
-        <v>46562</v>
-      </c>
+      <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -9076,9 +8589,7 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A315" s="13">
-        <v>46563</v>
-      </c>
+      <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -9100,9 +8611,7 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A316" s="13">
-        <v>46564</v>
-      </c>
+      <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -9124,9 +8633,7 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A317" s="13">
-        <v>46565</v>
-      </c>
+      <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -9148,9 +8655,7 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A318" s="13">
-        <v>46566</v>
-      </c>
+      <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -9172,9 +8677,7 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A319" s="13">
-        <v>46567</v>
-      </c>
+      <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -9196,9 +8699,7 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A320" s="13">
-        <v>46568</v>
-      </c>
+      <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -9220,9 +8721,7 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A321" s="13">
-        <v>46569</v>
-      </c>
+      <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -9244,9 +8743,7 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A322" s="13">
-        <v>46570</v>
-      </c>
+      <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -9268,9 +8765,7 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A323" s="13">
-        <v>46571</v>
-      </c>
+      <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -9292,9 +8787,7 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A324" s="13">
-        <v>46572</v>
-      </c>
+      <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -9316,9 +8809,7 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A325" s="13">
-        <v>46573</v>
-      </c>
+      <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -9340,9 +8831,7 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A326" s="13">
-        <v>46574</v>
-      </c>
+      <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -9364,9 +8853,7 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A327" s="13">
-        <v>46575</v>
-      </c>
+      <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -9388,9 +8875,7 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A328" s="13">
-        <v>46576</v>
-      </c>
+      <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -9412,9 +8897,7 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A329" s="13">
-        <v>46577</v>
-      </c>
+      <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -9436,9 +8919,7 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A330" s="13">
-        <v>46578</v>
-      </c>
+      <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -9460,9 +8941,7 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A331" s="13">
-        <v>46579</v>
-      </c>
+      <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -9484,9 +8963,7 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A332" s="13">
-        <v>46580</v>
-      </c>
+      <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -9508,9 +8985,7 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A333" s="13">
-        <v>46581</v>
-      </c>
+      <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -9532,9 +9007,7 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A334" s="13">
-        <v>46582</v>
-      </c>
+      <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -9556,9 +9029,7 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A335" s="13">
-        <v>46583</v>
-      </c>
+      <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -9580,9 +9051,7 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A336" s="13">
-        <v>46584</v>
-      </c>
+      <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -9604,9 +9073,7 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A337" s="13">
-        <v>46585</v>
-      </c>
+      <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -9628,9 +9095,7 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A338" s="13">
-        <v>46586</v>
-      </c>
+      <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -9652,9 +9117,7 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A339" s="13">
-        <v>46587</v>
-      </c>
+      <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -9676,9 +9139,7 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A340" s="13">
-        <v>46588</v>
-      </c>
+      <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -9700,9 +9161,7 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A341" s="13">
-        <v>46589</v>
-      </c>
+      <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -9724,9 +9183,7 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A342" s="13">
-        <v>46590</v>
-      </c>
+      <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -9748,9 +9205,7 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A343" s="13">
-        <v>46591</v>
-      </c>
+      <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -9772,9 +9227,7 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A344" s="13">
-        <v>46592</v>
-      </c>
+      <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -9796,9 +9249,7 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A345" s="13">
-        <v>46593</v>
-      </c>
+      <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -9820,9 +9271,7 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A346" s="13">
-        <v>46594</v>
-      </c>
+      <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -9844,9 +9293,7 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A347" s="13">
-        <v>46595</v>
-      </c>
+      <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -9868,9 +9315,7 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A348" s="13">
-        <v>46596</v>
-      </c>
+      <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -9892,9 +9337,7 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A349" s="13">
-        <v>46597</v>
-      </c>
+      <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -9916,9 +9359,7 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A350" s="13">
-        <v>46598</v>
-      </c>
+      <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -9940,9 +9381,7 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A351" s="13">
-        <v>46599</v>
-      </c>
+      <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -9964,9 +9403,7 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A352" s="13">
-        <v>46600</v>
-      </c>
+      <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -9988,9 +9425,7 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A353" s="13">
-        <v>46601</v>
-      </c>
+      <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -10012,9 +9447,7 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A354" s="13">
-        <v>46602</v>
-      </c>
+      <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -10036,9 +9469,7 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A355" s="13">
-        <v>46603</v>
-      </c>
+      <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -10060,9 +9491,7 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A356" s="13">
-        <v>46604</v>
-      </c>
+      <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -10084,9 +9513,7 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A357" s="13">
-        <v>46605</v>
-      </c>
+      <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -10108,9 +9535,7 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A358" s="13">
-        <v>46606</v>
-      </c>
+      <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -10132,9 +9557,7 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A359" s="13">
-        <v>46607</v>
-      </c>
+      <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -10156,9 +9579,7 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A360" s="13">
-        <v>46608</v>
-      </c>
+      <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -10180,9 +9601,7 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A361" s="13">
-        <v>46609</v>
-      </c>
+      <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -10204,9 +9623,7 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A362" s="13">
-        <v>46610</v>
-      </c>
+      <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -10228,9 +9645,7 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A363" s="13">
-        <v>46611</v>
-      </c>
+      <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -10252,9 +9667,7 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A364" s="13">
-        <v>46612</v>
-      </c>
+      <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -10276,9 +9689,7 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A365" s="13">
-        <v>46613</v>
-      </c>
+      <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -10300,9 +9711,7 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A366" s="13">
-        <v>46614</v>
-      </c>
+      <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -10324,9 +9733,7 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A367" s="13">
-        <v>46615</v>
-      </c>
+      <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -10348,9 +9755,7 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A368" s="13">
-        <v>46616</v>
-      </c>
+      <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -10372,9 +9777,7 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A369" s="13">
-        <v>46617</v>
-      </c>
+      <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -10396,9 +9799,7 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A370" s="13">
-        <v>46618</v>
-      </c>
+      <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -10420,9 +9821,7 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A371" s="13">
-        <v>46619</v>
-      </c>
+      <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -10444,9 +9843,7 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A372" s="13">
-        <v>46620</v>
-      </c>
+      <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -10468,9 +9865,7 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A373" s="13">
-        <v>46621</v>
-      </c>
+      <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -10492,9 +9887,7 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A374" s="13">
-        <v>46622</v>
-      </c>
+      <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -10516,9 +9909,7 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A375" s="13">
-        <v>46623</v>
-      </c>
+      <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -10540,9 +9931,7 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A376" s="13">
-        <v>46624</v>
-      </c>
+      <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -10564,9 +9953,7 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A377" s="13">
-        <v>46625</v>
-      </c>
+      <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -10588,9 +9975,7 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A378" s="13">
-        <v>46626</v>
-      </c>
+      <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -10612,9 +9997,7 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A379" s="13">
-        <v>46627</v>
-      </c>
+      <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -10636,9 +10019,7 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A380" s="13">
-        <v>46628</v>
-      </c>
+      <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -10660,9 +10041,7 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A381" s="13">
-        <v>46629</v>
-      </c>
+      <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -10684,9 +10063,7 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A382" s="13">
-        <v>46630</v>
-      </c>
+      <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -10708,9 +10085,7 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A383" s="13">
-        <v>46631</v>
-      </c>
+      <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -10732,9 +10107,7 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A384" s="13">
-        <v>46632</v>
-      </c>
+      <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -10756,9 +10129,7 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A385" s="13">
-        <v>46633</v>
-      </c>
+      <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -10780,9 +10151,7 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A386" s="13">
-        <v>46634</v>
-      </c>
+      <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -10804,9 +10173,7 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A387" s="13">
-        <v>46635</v>
-      </c>
+      <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -10828,9 +10195,7 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A388" s="13">
-        <v>46636</v>
-      </c>
+      <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -10852,9 +10217,7 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A389" s="13">
-        <v>46637</v>
-      </c>
+      <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -10876,9 +10239,7 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A390" s="13">
-        <v>46638</v>
-      </c>
+      <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -10900,9 +10261,7 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A391" s="13">
-        <v>46639</v>
-      </c>
+      <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -10924,9 +10283,7 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A392" s="13">
-        <v>46640</v>
-      </c>
+      <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -10948,9 +10305,7 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A393" s="13">
-        <v>46641</v>
-      </c>
+      <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -10972,9 +10327,7 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A394" s="13">
-        <v>46642</v>
-      </c>
+      <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -10996,9 +10349,7 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A395" s="13">
-        <v>46643</v>
-      </c>
+      <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -11020,9 +10371,7 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A396" s="13">
-        <v>46644</v>
-      </c>
+      <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -11044,9 +10393,7 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A397" s="13">
-        <v>46645</v>
-      </c>
+      <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -11068,9 +10415,7 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A398" s="13">
-        <v>46646</v>
-      </c>
+      <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -11092,9 +10437,7 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A399" s="13">
-        <v>46647</v>
-      </c>
+      <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -11116,9 +10459,7 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A400" s="13">
-        <v>46648</v>
-      </c>
+      <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -11140,9 +10481,7 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A401" s="13">
-        <v>46649</v>
-      </c>
+      <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FEBAC0-FF83-494C-A67C-F7FC3C2BCB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7389A5-FD02-4CCC-B31C-9A42B6F062A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,16 +17,11 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -109,6 +104,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
@@ -121,13 +119,39 @@
     <t>Name:</t>
   </si>
   <si>
+    <t>Krishna Kumar</t>
+  </si>
+  <si>
     <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>CAP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>776 D1P2632</t>
+    </r>
+  </si>
+  <si>
     <t>Month:</t>
+  </si>
+  <si>
+    <t>AUGUST</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -187,47 +211,16 @@
     <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
-    <t>5. GOOD PRACTICE</t>
+    <t>Neutral</t>
   </si>
   <si>
-    <t>Krishna Kumar</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>CAP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>776 D1P2632</t>
-    </r>
-  </si>
-  <si>
-    <t>AUGUST</t>
+    <t>High</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
     <t>Today I notice myself and learn what is the right way of self study.</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Excellent</t>
@@ -270,9 +263,6 @@
   </si>
   <si>
     <t>Experience</t>
-  </si>
-  <si>
-    <t>o</t>
   </si>
 </sst>
 </file>
@@ -337,6 +327,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
@@ -365,17 +361,9 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -398,7 +386,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -421,11 +409,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -433,22 +432,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -457,7 +456,7 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -466,14 +465,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -676,13 +678,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -911,17 +913,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
@@ -937,7 +939,7 @@
       <c r="A39" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180550000000002" footer="0.51180550000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
@@ -959,117 +961,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+        <v>31</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="22">
+        <v>33</v>
+      </c>
+      <c r="F2" s="23">
         <v>12620172</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+        <v>34</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="22"/>
+        <v>36</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -1106,16 +1108,16 @@
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -1152,13 +1154,13 @@
         <v>540</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1196,13 +1198,13 @@
         <v>540</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N8" s="17"/>
     </row>
@@ -1240,13 +1242,13 @@
         <v>540</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1284,13 +1286,13 @@
         <v>415</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1366,16 +1368,16 @@
         <v>235</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1412,13 +1414,13 @@
         <v>428</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N13" s="17"/>
     </row>
@@ -1459,7 +1461,7 @@
         <v>61</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
@@ -1496,13 +1498,13 @@
         <v>965</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1546,7 +1548,7 @@
         <v>62</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>63</v>
@@ -1589,10 +1591,10 @@
         <v>61</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>64</v>
@@ -1632,13 +1634,13 @@
         <v>250</v>
       </c>
       <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="M18" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>65</v>
@@ -1678,13 +1680,13 @@
         <v>465</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>64</v>
@@ -1730,7 +1732,7 @@
         <v>62</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>66</v>
@@ -1770,13 +1772,13 @@
         <v>350</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N21" s="17" t="s">
         <v>64</v>
@@ -1816,13 +1818,13 @@
         <v>380</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N22" s="17" t="s">
         <v>64</v>
@@ -1862,13 +1864,13 @@
         <v>505</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N23" s="17" t="s">
         <v>64</v>
@@ -1911,10 +1913,10 @@
         <v>61</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N24" s="17" t="s">
         <v>64</v>
@@ -1954,13 +1956,13 @@
         <v>410</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N25" s="17" t="s">
         <v>64</v>
@@ -2006,7 +2008,7 @@
         <v>68</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N26" s="17" t="s">
         <v>69</v>
@@ -2046,13 +2048,13 @@
         <v>570</v>
       </c>
       <c r="K27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="N27" s="17" t="s">
         <v>70</v>
@@ -2098,7 +2100,7 @@
         <v>71</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N28" s="17" t="s">
         <v>72</v>
@@ -2144,7 +2146,7 @@
         <v>62</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N29" s="17" t="s">
         <v>73</v>
@@ -2190,7 +2192,7 @@
         <v>62</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N30" s="17" t="s">
         <v>73</v>
@@ -2230,13 +2232,13 @@
         <v>250</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N31" s="17" t="s">
         <v>64</v>
@@ -2276,13 +2278,13 @@
         <v>695</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>68</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N32" s="17" t="s">
         <v>74</v>
@@ -2322,13 +2324,13 @@
         <v>110</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N33" s="17" t="s">
         <v>64</v>
@@ -2368,13 +2370,13 @@
         <v>440</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N34" s="17" t="s">
         <v>64</v>
@@ -2414,13 +2416,13 @@
         <v>335</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N35" s="17" t="s">
         <v>64</v>
@@ -2445,8 +2447,8 @@
       <c r="F36" s="14">
         <v>0</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>75</v>
+      <c r="G36" s="14">
+        <v>0</v>
       </c>
       <c r="H36" s="14">
         <v>60</v>
@@ -2460,127 +2462,247 @@
         <v>570</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N36" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B37" s="18">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>360</v>
+      </c>
+      <c r="E37" s="14">
+        <v>90</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>50</v>
+      </c>
+      <c r="I37" s="15">
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>1010</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>40</v>
+      </c>
+      <c r="D38" s="14">
+        <v>420</v>
+      </c>
+      <c r="E38" s="14">
+        <v>50</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>30</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B39" s="14">
+        <v>360</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>360</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>420</v>
+      </c>
+      <c r="G39" s="14">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>30</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>180</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>25</v>
+      </c>
+      <c r="D40" s="14">
+        <v>170</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>420</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>25</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B41" s="14">
+        <v>360</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>50</v>
+      </c>
+      <c r="F41" s="14">
+        <v>180</v>
+      </c>
+      <c r="G41" s="14">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14">
+        <v>50</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>
@@ -10512,25 +10634,22 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180550000000002" footer="0.51180550000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7389A5-FD02-4CCC-B31C-9A42B6F062A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7276ACE-204A-4000-8793-32DBDB1DE938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,18 @@
   </si>
   <si>
     <t>Experience</t>
+  </si>
+  <si>
+    <t>Today i am feelinging very upset because some of student's are tried to demolish the our college reputation as well as his architechure.</t>
+  </si>
+  <si>
+    <t>Crazy ruckus on campus today by some unknown people. Seeing all the videos on social media and hearing what happened has left me really upset and a bit scared. Hoping things calm down soon.</t>
+  </si>
+  <si>
+    <t>I am going to home.</t>
+  </si>
+  <si>
+    <t>Today I reached my home state.</t>
   </si>
 </sst>
 </file>
@@ -2705,114 +2717,234 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B42" s="14">
+        <v>390</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>240</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>30</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B43" s="14">
+        <v>360</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>50</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>40</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B44" s="14">
+        <v>60</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>60</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>120</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>1320</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B45" s="14">
+        <v>180</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>0</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>180</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>1260</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B46" s="14">
+        <v>300</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>0</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>50</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>1090</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
